--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487456_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487456_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9074</v>
+        <v>4.4671</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1644</v>
+        <v>-0.1691</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7431</v>
+        <v>4.6362</v>
       </c>
       <c r="G2" t="n">
         <v>3.9933</v>
@@ -610,13 +610,13 @@
         <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6768</v>
+        <v>0.2364</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4176</v>
+        <v>-0.7511</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0944</v>
+        <v>0.9875</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5638</v>
+        <v>2.6213</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2898</v>
+        <v>0.775</v>
       </c>
       <c r="F3" t="n">
-        <v>2.274</v>
+        <v>1.8463</v>
       </c>
       <c r="G3" t="n">
         <v>-0.656</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5112</v>
+        <v>0.5687</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8734</v>
+        <v>-0.3882</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3846</v>
+        <v>0.9569</v>
       </c>
       <c r="V3" t="n">
         <v>2.7086</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5255</v>
+        <v>2.4154</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.1592</v>
+        <v>-2.8951</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6847</v>
+        <v>5.3105</v>
       </c>
       <c r="G4" t="n">
         <v>2.3135</v>
@@ -766,13 +766,13 @@
         <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0958</v>
+        <v>-0.0144</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8446</v>
+        <v>-0.5805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9403</v>
+        <v>0.5661</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8818</v>
+        <v>1.2574</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9799</v>
+        <v>-2.8182</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8617</v>
+        <v>4.0756</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2419</v>
@@ -844,13 +844,13 @@
         <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4419</v>
+        <v>-1.0663</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1286</v>
+        <v>-0.9669</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3132</v>
+        <v>-0.0994</v>
       </c>
       <c r="V5" t="n">
         <v>0.9988</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>C. CAAMAÑO ARAGUNDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3928</v>
+        <v>0.3333</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9556</v>
+        <v>-0.4217</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3484</v>
+        <v>0.755</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1315</v>
+        <v>1.4849</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6714</v>
+        <v>1.8942</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4601</v>
+        <v>-0.4093</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5712</v>
+        <v>0.6652</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5308</v>
+        <v>1.3474</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>-0.6822</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5603</v>
+        <v>0.8197</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1406</v>
+        <v>0.5468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4197</v>
+        <v>0.2729</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1242</v>
+        <v>0.065</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4317</v>
+        <v>-0.1076</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3075</v>
+        <v>0.1726</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3293</v>
+        <v>0.3044</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8573</v>
+        <v>-2.4909</v>
       </c>
       <c r="F7" t="n">
-        <v>2.528</v>
+        <v>2.7953</v>
       </c>
       <c r="G7" t="n">
         <v>0.6714</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0386</v>
+        <v>-0.4049</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0098</v>
+        <v>-0.6434</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0288</v>
+        <v>0.2385</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9412</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. CAAMAÑO ARAGUNDE</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3434</v>
+        <v>0.0475</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-1.4079</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4877</v>
+        <v>1.4554</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4849</v>
+        <v>1.1315</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8942</v>
+        <v>0.6714</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4093</v>
+        <v>0.4601</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6652</v>
+        <v>0.5712</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3474</v>
+        <v>0.5308</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6822</v>
+        <v>0.0404</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8197</v>
+        <v>0.5603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5468</v>
+        <v>0.1406</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2729</v>
+        <v>0.4197</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6117</v>
+        <v>-0.2211</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.517</v>
+        <v>-0.0206</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.2005</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2301</v>
+        <v>-1.3622</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7519</v>
+        <v>-3.2859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5218</v>
+        <v>1.9237</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5352</v>
+        <v>0.2443</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1926</v>
+        <v>-0.4383</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7278</v>
+        <v>0.6826</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0293</v>
+        <v>-0.3212</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3322</v>
+        <v>-0.4425</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3029</v>
+        <v>0.1212</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5645</v>
+        <v>0.5655</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1396</v>
+        <v>0.0042</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4249</v>
+        <v>0.5614</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7474</v>
+        <v>-0.0397</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2358</v>
+        <v>-0.3023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.2626</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7086</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8323</v>
+        <v>-1.7696</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9164</v>
+        <v>-2.4518</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0841</v>
+        <v>0.6822</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2443</v>
+        <v>0.5352</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4383</v>
+        <v>-1.1926</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6826</v>
+        <v>1.7278</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3212</v>
+        <v>-0.0293</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4425</v>
+        <v>-1.3322</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1212</v>
+        <v>1.3029</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5655</v>
+        <v>0.5645</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0042</v>
+        <v>0.1396</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5614</v>
+        <v>0.4249</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5098</v>
+        <v>0.2079</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9328</v>
+        <v>-0.464</v>
       </c>
       <c r="U10" t="n">
-        <v>0.423</v>
+        <v>0.672</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2754</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8704</v>
+        <v>-5.7576</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5957</v>
+        <v>-3.5363</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2747</v>
+        <v>-2.2213</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7109</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6884</v>
+        <v>-0.5755</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4752</v>
+        <v>-0.4158</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2131</v>
+        <v>-0.1597</v>
       </c>
       <c r="V11" t="n">
         <v>-1.492</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.665799999999999</v>
+        <v>2.557</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.5929</v>
+        <v>-18.7019</v>
       </c>
       <c r="F12" t="n">
-        <v>21.2588</v>
+        <v>21.2589</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7653</v>
+        <v>6.765299999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6874000000000003</v>
+        <v>-0.6874000000000002</v>
       </c>
       <c r="I12" t="n">
         <v>7.4526</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4589000000000003</v>
+        <v>0.4589000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-2.0884</v>
       </c>
       <c r="L12" t="n">
-        <v>2.547199999999999</v>
+        <v>2.5472</v>
       </c>
       <c r="M12" t="n">
         <v>6.3062</v>
@@ -1381,7 +1381,7 @@
         <v>4.9054</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9792000000000002</v>
+        <v>-0.9792000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.6056</v>
@@ -1390,10 +1390,10 @@
         <v>17.6261</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.135</v>
+        <v>-1.2439</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.5315</v>
+        <v>-4.640400000000001</v>
       </c>
       <c r="U12" t="n">
         <v>3.3966</v>
@@ -1405,7 +1405,7 @@
         <v>4.0854</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.0708</v>
+        <v>-6.070799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0289</v>
+        <v>6.02</v>
       </c>
       <c r="E13" t="n">
-        <v>0.743</v>
+        <v>1.357</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2859</v>
+        <v>4.663</v>
       </c>
       <c r="G13" t="n">
         <v>3.3027</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.92</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0757</v>
+        <v>-0.4617</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1557</v>
+        <v>0.5327</v>
       </c>
       <c r="V13" t="n">
         <v>0.8837</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.4728</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.4762</v>
+        <v>-2.2174</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4152</v>
+        <v>3.6903</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5589</v>
+        <v>-0.4248</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9122</v>
+        <v>-1.096</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3534</v>
+        <v>0.6711</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4673</v>
+        <v>-1.9413</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1091</v>
+        <v>-1.6469</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6418</v>
+        <v>-0.2944</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0916</v>
+        <v>1.5165</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1969</v>
+        <v>0.551</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2885</v>
+        <v>0.9655</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3502</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>1.614</v>
+        <v>0.0935</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.5134</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9159</v>
+        <v>0.607</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3329</v>
+        <v>1.2166</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7269</v>
+        <v>0.679</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.9338</v>
+        <v>-0.1128</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6607</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4248</v>
+        <v>-0.0357</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.096</v>
+        <v>0.737</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6711</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9413</v>
+        <v>0.2842</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6469</v>
+        <v>0.1225</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2944</v>
+        <v>0.1617</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5165</v>
+        <v>-0.3198</v>
       </c>
       <c r="N15" t="n">
-        <v>0.551</v>
+        <v>0.6145</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9655</v>
+        <v>-0.9344</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6524</v>
+        <v>-0.1056</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2298</v>
+        <v>-0.397</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5774</v>
+        <v>0.2914</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2166</v>
+        <v>-0.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3093</v>
+        <v>0.2181</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2152</v>
+        <v>-0.1743</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5245</v>
+        <v>0.3923</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0357</v>
+        <v>-0.2462</v>
       </c>
       <c r="H16" t="n">
-        <v>0.737</v>
+        <v>-0.2514</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.0052</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2842</v>
+        <v>0.0204</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1225</v>
+        <v>0.0204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1617</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3198</v>
+        <v>-0.2667</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6145</v>
+        <v>-0.2719</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9344</v>
+        <v>0.0052</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4752</v>
+        <v>0.0726</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4993</v>
+        <v>-0.1947</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0241</v>
+        <v>0.2673</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1692</v>
+        <v>0.1987</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2766</v>
+        <v>-3.1926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4458</v>
+        <v>3.3913</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2462</v>
+        <v>0.5589</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2514</v>
+        <v>0.9122</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0052</v>
+        <v>-0.3534</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0204</v>
+        <v>0.4673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0204</v>
+        <v>1.1091</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.6418</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2667</v>
+        <v>0.0916</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2719</v>
+        <v>-0.1969</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0052</v>
+        <v>0.2885</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0238</v>
+        <v>0.8737</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.297</v>
+        <v>-0.0182</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3208</v>
+        <v>0.8919</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3706</v>
+        <v>-0.4259</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9528</v>
+        <v>-3.8504</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5821</v>
+        <v>3.4246</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1489</v>
@@ -1858,13 +1858,13 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.398</v>
+        <v>0.3427</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5893</v>
+        <v>-0.487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9873</v>
+        <v>0.8297</v>
       </c>
       <c r="V18" t="n">
         <v>2.318</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5593</v>
+        <v>-0.6036</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2917</v>
+        <v>-3.4964</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7325</v>
+        <v>2.8928</v>
       </c>
       <c r="G19" t="n">
         <v>-4.9289</v>
@@ -1936,13 +1936,13 @@
         <v>3.1336</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2041</v>
+        <v>-0.4088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9274</v>
+        <v>1.0878</v>
       </c>
       <c r="V19" t="n">
         <v>1.492</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.6543</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0978</v>
+        <v>-1.9955</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1245</v>
+        <v>1.3412</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6913</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.457</v>
+        <v>-0.1381</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3982</v>
+        <v>-0.2958</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0589</v>
+        <v>0.1578</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.47</v>
+        <v>-1.5631</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3536</v>
+        <v>-1.6607</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1163</v>
+        <v>0.0975</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9554</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2308</v>
+        <v>0.1376</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1141</v>
+        <v>-0.4211</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3449</v>
+        <v>0.5587</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9412</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4662</v>
+        <v>-6.3254</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.404</v>
+        <v>-5.9157</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0622</v>
+        <v>-0.4097</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1955</v>
@@ -2170,13 +2170,13 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6498</v>
+        <v>0.7906</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3129</v>
+        <v>-0.1988</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3369</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7662</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.666099999999999</v>
+        <v>-0.9836999999999989</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.2587</v>
+        <v>-21.2588</v>
       </c>
       <c r="F23" t="n">
-        <v>19.5927</v>
+        <v>20.2751</v>
       </c>
       <c r="G23" t="n">
         <v>-6.765099999999999</v>
@@ -2218,7 +2218,7 @@
         <v>0.6874000000000002</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.4527</v>
+        <v>-7.452699999999999</v>
       </c>
       <c r="J23" t="n">
         <v>-6.3063</v>
@@ -2230,16 +2230,16 @@
         <v>-4.9054</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4591000000000003</v>
+        <v>-0.4590999999999998</v>
       </c>
       <c r="N23" t="n">
-        <v>2.0882</v>
+        <v>2.088200000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-2.5473</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9791000000000007</v>
+        <v>0.9791000000000003</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.6263</v>
@@ -2248,19 +2248,19 @@
         <v>18.6056</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1351</v>
+        <v>2.817</v>
       </c>
       <c r="T23" t="n">
         <v>-3.3965</v>
       </c>
       <c r="U23" t="n">
-        <v>5.5315</v>
+        <v>6.213699999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.9851</v>
       </c>
       <c r="W23" t="n">
-        <v>6.070500000000001</v>
+        <v>6.0705</v>
       </c>
       <c r="X23" t="n">
         <v>-4.0854</v>
